--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/responsible_ai_controls.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/responsible_ai_controls.xlsx
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tomas Halvorsen</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -506,12 +506,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Elena Vasquez</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Raymond Okafor</t>
+          <t>Aisha Bello</t>
         </is>
       </c>
     </row>
@@ -550,12 +550,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Implemented</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Aisha Bello</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Marcus Reilly</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Marcus Reilly</t>
+          <t>Maria Donnelly</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sofia Marchetti</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
@@ -682,12 +682,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Implemented</t>
+          <t>Planned</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Liam O'Sullivan</t>
+          <t>Raymond Okafor</t>
         </is>
       </c>
     </row>
